--- a/public/static/销售报价导入模板.xlsx
+++ b/public/static/销售报价导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="销售报价" sheetId="1" r:id="rId1"/>
@@ -28,60 +28,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>序号</t>
   </si>
   <si>
-    <t>客户物料号(必填)</t>
+    <t>客户货号(必填)</t>
   </si>
   <si>
-    <t>客户图号</t>
-  </si>
-  <si>
-    <t>物料描述</t>
-  </si>
-  <si>
-    <t>规格型号</t>
-  </si>
-  <si>
-    <t>单位</t>
+    <t>规格型号(必填)</t>
   </si>
   <si>
     <t>数量(必填)</t>
   </si>
   <si>
-    <t>牌价(含税)</t>
-  </si>
-  <si>
     <t>单价(含税)</t>
-  </si>
-  <si>
-    <t>单价(不含税)</t>
   </si>
   <si>
     <t>税率(%)</t>
   </si>
   <si>
-    <t>备注1</t>
-  </si>
-  <si>
-    <t>备注2</t>
+    <t>备注</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>001</t>
   </si>
   <si>
     <t>100</t>
   </si>
   <si>
     <t xml:space="preserve">说明：
-1、单价含税与不含税选填一项，填写含税单价，自动计算不含税单价，填写含税单价，自动计算含税单价
-2、税率如果未填写，默认为13%
-3、牌价值可以通过导入获取牌价功能获取
+1、税率如果未填写，默认为13%
 </t>
   </si>
 </sst>
@@ -758,7 +735,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -771,19 +748,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1319,15 +1293,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="8" width="20" customWidth="1"/>
-    <col min="9" max="10" width="20" style="2" customWidth="1"/>
-    <col min="11" max="13" width="20" customWidth="1"/>
+    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
+    <col min="2" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="20" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.2222222222222" customWidth="1"/>
+    <col min="7" max="7" width="29.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:13">
+    <row r="1" ht="25" customHeight="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1340,7 +1316,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1349,45 +1325,19 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:7">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:13">
-      <c r="A2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1399,14 +1349,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="131.775" customWidth="1"/>
+    <col min="1" max="1" width="131.777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1"/>

--- a/public/static/销售报价导入模板.xlsx
+++ b/public/static/销售报价导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="销售报价" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>序号</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>100</t>
   </si>
   <si>
     <t xml:space="preserve">说明：
@@ -1297,14 +1294,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
+    <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.2222222222222" customWidth="1"/>
-    <col min="7" max="7" width="22.1111111111111" customWidth="1"/>
-    <col min="8" max="8" width="29.1111111111111" customWidth="1"/>
+    <col min="6" max="6" width="13.225" customWidth="1"/>
+    <col min="7" max="7" width="22.1083333333333" customWidth="1"/>
+    <col min="8" max="8" width="29.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:8">
@@ -1340,9 +1337,7 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="E2" s="7"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -1357,14 +1352,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="131.777777777778" customWidth="1"/>
+    <col min="1" max="1" width="131.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1"/>

--- a/public/static/销售报价导入模板.xlsx
+++ b/public/static/销售报价导入模板.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>序号</t>
   </si>
@@ -48,7 +48,28 @@
     <t>税率(%)</t>
   </si>
   <si>
-    <t>要求</t>
+    <t>打字内容</t>
+  </si>
+  <si>
+    <t>精度等级</t>
+  </si>
+  <si>
+    <t>振动等级</t>
+  </si>
+  <si>
+    <t>油脂</t>
+  </si>
+  <si>
+    <t>油脂量</t>
+  </si>
+  <si>
+    <t>游隙</t>
+  </si>
+  <si>
+    <t>包装方式</t>
+  </si>
+  <si>
+    <t>特殊要求</t>
   </si>
   <si>
     <t>备注</t>
@@ -1293,18 +1314,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.225" customWidth="1"/>
-    <col min="7" max="7" width="22.1083333333333" customWidth="1"/>
-    <col min="8" max="8" width="29.1083333333333" customWidth="1"/>
+    <col min="6" max="11" width="13.225" customWidth="1"/>
+    <col min="12" max="14" width="14.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="29.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:8">
+    <row r="1" ht="25" customHeight="1" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1329,10 +1350,31 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:8">
+    <row r="2" ht="20" customHeight="1" spans="1:15">
       <c r="A2" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1341,6 +1383,13 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1359,7 +1408,7 @@
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1"/>
